--- a/Manual/source/tab/connectors.xlsx
+++ b/Manual/source/tab/connectors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="48"/>
   </bookViews>
   <sheets>
     <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId3"/>
@@ -1238,6 +1238,15 @@
     <t xml:space="preserve">Analogová zem</t>
   </si>
   <si>
+    <t xml:space="preserve">PT1000_2+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vstup pro 2. PT1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PT1000_2-</t>
+  </si>
+  <si>
     <t xml:space="preserve">PT1000_1+</t>
   </si>
   <si>
@@ -1245,15 +1254,6 @@
   </si>
   <si>
     <t xml:space="preserve">PT1000_1-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PT1000_2+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vstup pro 2. PT1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PT1000_2-</t>
   </si>
   <si>
     <t xml:space="preserve">DITTL1</t>

--- a/Manual/source/tab/connectors.xlsx
+++ b/Manual/source/tab/connectors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="48"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="19"/>
   </bookViews>
   <sheets>
     <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId3"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="445">
   <si>
     <t xml:space="preserve">Toto je sešit se zdrojovými tabulkami popisu konektorů TGZ/TGS v češtině. Každý list odpovídá jednomu unikátnímu typu konektoru. Jelikož se často konektory v rámci TGZ opakují (typicky ty na řídicií desce), jsou zde jen jednou. Tj. Např. IO konektor 22pin weidmuller B2CF se používá pořád dokola, je zde tedy zanesen jen jednou jako „X8_IO_22pin_B2CF“</t>
   </si>
@@ -819,6 +819,9 @@
   </si>
   <si>
     <t xml:space="preserve">0,13 ~ 2,5 mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+B2</t>
   </si>
   <si>
     <t xml:space="preserve">+ Brzda motor 2</t>
@@ -7909,12 +7912,11 @@
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="str">
-        <f aca="false">+B2</f>
-        <v>-B2</v>
+      <c r="B3" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>236</v>
@@ -7928,7 +7930,7 @@
         <v>225</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>236</v>
@@ -7942,7 +7944,7 @@
         <v>226</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>236</v>
@@ -7953,10 +7955,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>236</v>
@@ -7967,10 +7969,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>236</v>
@@ -8026,10 +8028,10 @@
         <v>115</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8037,13 +8039,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8057,7 +8059,7 @@
         <v>120</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8071,7 +8073,7 @@
         <v>111</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8085,7 +8087,7 @@
         <v>114</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -8135,10 +8137,10 @@
         <v>115</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8146,13 +8148,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8163,10 +8165,10 @@
         <v>226</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8177,10 +8179,10 @@
         <v>225</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -8230,10 +8232,10 @@
         <v>173</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8244,10 +8246,10 @@
         <v>173</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8258,10 +8260,10 @@
         <v>173</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8272,10 +8274,10 @@
         <v>119</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -8322,13 +8324,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8336,13 +8338,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -8394,7 +8396,7 @@
         <v>205</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8408,7 +8410,7 @@
         <v>208</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8422,7 +8424,7 @@
         <v>210</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8436,7 +8438,7 @@
         <v>212</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8450,7 +8452,7 @@
         <v>214</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8464,7 +8466,7 @@
         <v>216</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8527,10 +8529,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>206</v>
@@ -8541,10 +8543,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>206</v>
@@ -8555,10 +8557,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>206</v>
@@ -8569,10 +8571,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>206</v>
@@ -8583,10 +8585,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>206</v>
@@ -8597,10 +8599,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>206</v>
@@ -8611,7 +8613,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>210</v>
@@ -8625,10 +8627,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>206</v>
@@ -8639,10 +8641,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>206</v>
@@ -8695,10 +8697,10 @@
         <v>121</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8712,7 +8714,7 @@
         <v>125</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8726,7 +8728,7 @@
         <v>210</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -8778,7 +8780,7 @@
         <v>205</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8792,7 +8794,7 @@
         <v>208</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8806,7 +8808,7 @@
         <v>210</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8820,7 +8822,7 @@
         <v>212</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8834,7 +8836,7 @@
         <v>214</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8848,7 +8850,7 @@
         <v>216</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8911,10 +8913,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>206</v>
@@ -8925,10 +8927,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>206</v>
@@ -8939,10 +8941,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>206</v>
@@ -8953,10 +8955,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>206</v>
@@ -8967,10 +8969,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>206</v>
@@ -8981,10 +8983,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>206</v>
@@ -8995,10 +8997,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>206</v>
@@ -9009,10 +9011,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>206</v>
@@ -9023,7 +9025,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>210</v>
@@ -9037,10 +9039,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>206</v>
@@ -9051,10 +9053,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>206</v>
@@ -9211,13 +9213,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9225,13 +9227,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9504,10 +9506,10 @@
         <v>204</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9518,10 +9520,10 @@
         <v>207</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9529,13 +9531,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9543,13 +9545,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9601,10 +9603,10 @@
         <v>204</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9615,10 +9617,10 @@
         <v>207</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9626,13 +9628,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9640,13 +9642,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9707,10 +9709,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>123</v>
@@ -9721,10 +9723,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>123</v>
@@ -9773,13 +9775,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9787,13 +9789,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9801,13 +9803,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>210</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9815,13 +9817,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9829,13 +9831,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9843,13 +9845,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9857,13 +9859,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9871,13 +9873,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9936,10 +9938,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>112</v>
@@ -9950,10 +9952,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>112</v>
@@ -9964,10 +9966,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>112</v>
@@ -9978,10 +9980,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>112</v>
@@ -10031,13 +10033,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10045,13 +10047,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10059,13 +10061,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10073,13 +10075,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -10122,7 +10124,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>166</v>
@@ -10133,7 +10135,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>164</v>
@@ -10144,7 +10146,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>162</v>
@@ -10155,7 +10157,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>160</v>
@@ -10166,7 +10168,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>158</v>
@@ -10177,7 +10179,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>156</v>
@@ -10188,7 +10190,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>154</v>
@@ -10199,7 +10201,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>152</v>
@@ -10210,10 +10212,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10221,10 +10223,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10337,7 +10339,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>166</v>
@@ -10348,7 +10350,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>164</v>
@@ -10359,7 +10361,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>162</v>
@@ -10370,7 +10372,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>160</v>
@@ -10381,7 +10383,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>158</v>
@@ -10392,7 +10394,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>156</v>
@@ -10403,7 +10405,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>154</v>
@@ -10414,7 +10416,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>152</v>
@@ -10425,10 +10427,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10436,10 +10438,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10477,10 +10479,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>108</v>
@@ -10488,24 +10490,24 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10584,10 +10586,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>112</v>
@@ -10598,10 +10600,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>112</v>
@@ -10615,7 +10617,7 @@
         <v>115</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>112</v>
@@ -10934,7 +10936,7 @@
         <v>182</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11067,7 +11069,7 @@
         <v>183</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11109,7 +11111,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>59</v>
@@ -11118,7 +11120,7 @@
         <v>200</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11126,7 +11128,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -11135,7 +11137,7 @@
         <v>198</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11143,7 +11145,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>192</v>
@@ -11152,7 +11154,7 @@
         <v>196</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11160,7 +11162,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>191</v>
@@ -11169,7 +11171,7 @@
         <v>194</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11220,7 +11222,7 @@
         <v>190</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11237,7 +11239,7 @@
         <v>188</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11316,7 +11318,7 @@
         <v>183</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11358,7 +11360,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>59</v>
@@ -11367,7 +11369,7 @@
         <v>200</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11375,7 +11377,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -11384,7 +11386,7 @@
         <v>198</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11392,7 +11394,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>192</v>
@@ -11401,7 +11403,7 @@
         <v>196</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11409,7 +11411,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>191</v>
@@ -11418,7 +11420,7 @@
         <v>194</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11531,7 +11533,7 @@
         <v>183</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11573,7 +11575,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>59</v>
@@ -11582,7 +11584,7 @@
         <v>200</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11590,7 +11592,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>59</v>
@@ -11599,7 +11601,7 @@
         <v>198</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11607,7 +11609,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>192</v>
@@ -11616,7 +11618,7 @@
         <v>196</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11624,7 +11626,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>191</v>
@@ -11633,7 +11635,7 @@
         <v>194</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11747,10 +11749,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11761,7 +11763,7 @@
         <v>126</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11769,10 +11771,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11780,10 +11782,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11791,10 +11793,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11802,10 +11804,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11813,10 +11815,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11827,7 +11829,7 @@
         <v>149</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11835,10 +11837,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11849,7 +11851,7 @@
         <v>149</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11857,10 +11859,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11871,7 +11873,7 @@
         <v>149</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12265,7 +12267,7 @@
         <v>165</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12276,7 +12278,7 @@
         <v>163</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12287,7 +12289,7 @@
         <v>161</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12298,7 +12300,7 @@
         <v>159</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12309,7 +12311,7 @@
         <v>157</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12320,7 +12322,7 @@
         <v>155</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12331,7 +12333,7 @@
         <v>153</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12342,7 +12344,7 @@
         <v>151</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12350,10 +12352,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12361,10 +12363,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12372,10 +12374,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12383,10 +12385,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12397,7 +12399,7 @@
         <v>143</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12408,7 +12410,7 @@
         <v>141</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12419,7 +12421,7 @@
         <v>139</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12430,7 +12432,7 @@
         <v>137</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12441,7 +12443,7 @@
         <v>135</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12452,7 +12454,7 @@
         <v>133</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -12495,10 +12497,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12506,10 +12508,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12517,10 +12519,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12528,10 +12530,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12539,10 +12541,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12550,10 +12552,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12561,10 +12563,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12572,10 +12574,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -12618,10 +12620,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12629,10 +12631,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12640,10 +12642,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12651,10 +12653,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12662,10 +12664,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12676,7 +12678,7 @@
         <v>119</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12684,10 +12686,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12695,10 +12697,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12706,10 +12708,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12717,10 +12719,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12772,10 +12774,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12783,10 +12785,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12794,10 +12796,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12805,10 +12807,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12816,10 +12818,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12827,10 +12829,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12838,10 +12840,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12849,10 +12851,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Manual/source/tab/connectors.xlsx
+++ b/Manual/source/tab/connectors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="59"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="60"/>
   </bookViews>
   <sheets>
     <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId3"/>
@@ -68,6 +68,10 @@
     <sheet name="X6_TGS560_50_DCbus" sheetId="58" state="visible" r:id="rId60"/>
     <sheet name="X4_TGS560_24V_5pin_BCZ" sheetId="59" state="visible" r:id="rId61"/>
     <sheet name="S1_TGS560_DIP" sheetId="60" state="visible" r:id="rId62"/>
+    <sheet name="LED_TGS560" sheetId="61" state="visible" r:id="rId63"/>
+    <sheet name="X4_ACIN_4pin_TGS560_25" sheetId="62" state="visible" r:id="rId64"/>
+    <sheet name="X1_DC_6pin_TGS560_25" sheetId="63" state="visible" r:id="rId65"/>
+    <sheet name="X5_RBR_3pin_TGS560_25" sheetId="64" state="visible" r:id="rId66"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -79,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="492">
   <si>
     <t xml:space="preserve">Toto je sešit se zdrojovými tabulkami popisu konektorů TGZ/TGS v češtině. Každý list odpovídá jednomu unikátnímu typu konektoru. Jelikož se často konektory v rámci TGZ opakují (typicky ty na řídicií desce), jsou zde jen jednou. Tj. Např. IO konektor 22pin weidmuller B2CF se používá pořád dokola, je zde tedy zanesen jen jednou jako „X8_IO_22pin_B2CF“</t>
   </si>
@@ -1533,19 +1537,64 @@
     <t xml:space="preserve">0001</t>
   </si>
   <si>
+    <t xml:space="preserve">Zvolený 4 bit. kód</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Význam – volba funkce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">výchozí nastavení</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rezervováno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Červená LED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Počet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Význam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">krátké bliknutí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">podpětí Dcbus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">přepětí Dcbus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chyba fázového napětí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vysoká interní teplota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vysoká teplota softstart modulu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vysoká teplota brzdného rezistoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zelená LED</t>
+  </si>
+  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">Zvolený 4 bit. kód</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Význam – volba funkce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brzdný odpor interní</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brzdný odpor 1 kW</t>
+    <t xml:space="preserve">trvalý svit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zařízení připraveno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trvale vypnuto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zařízení nepřipraveno</t>
   </si>
 </sst>
 </file>
@@ -1705,11 +1754,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14613,7 +14662,7 @@
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
@@ -14674,23 +14723,12 @@
         <v>471</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>472</v>
-      </c>
-    </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14698,7 +14736,7 @@
         <v>0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H8" s="14"/>
       <c r="I8" s="13"/>
@@ -14708,7 +14746,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="13"/>
@@ -14718,7 +14756,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H10" s="14"/>
       <c r="I10" s="13"/>
@@ -14728,7 +14766,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="13"/>
@@ -14738,7 +14776,7 @@
         <v>100</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H12" s="14"/>
       <c r="I12" s="13"/>
@@ -14748,7 +14786,7 @@
         <v>101</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="13"/>
@@ -14758,7 +14796,7 @@
         <v>110</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H14" s="14"/>
       <c r="I14" s="13"/>
@@ -14768,7 +14806,7 @@
         <v>111</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H15" s="14"/>
       <c r="I15" s="13"/>
@@ -14778,7 +14816,7 @@
         <v>1000</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="13"/>
@@ -14788,7 +14826,7 @@
         <v>1001</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H17" s="14"/>
       <c r="I17" s="13"/>
@@ -14798,7 +14836,7 @@
         <v>1010</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C18" s="10"/>
       <c r="H18" s="14"/>
@@ -14809,7 +14847,7 @@
         <v>1011</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="13"/>
@@ -14819,7 +14857,7 @@
         <v>1100</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="13"/>
@@ -14829,7 +14867,7 @@
         <v>1101</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="13"/>
@@ -14839,7 +14877,7 @@
         <v>1110</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="13"/>
@@ -14849,10 +14887,554 @@
         <v>1111</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H23" s="14"/>
       <c r="I23" s="13"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="H7" s="14"/>
+      <c r="I7" s="13"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="H8" s="14"/>
+      <c r="I8" s="13"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="H9" s="14"/>
+      <c r="I9" s="13"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="13"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="I11" s="14"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="I12" s="14"/>
+      <c r="J12" s="13"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="13"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I14" s="14"/>
+      <c r="J14" s="13"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I15" s="14"/>
+      <c r="J15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="14"/>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I17" s="14"/>
+      <c r="J17" s="13"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I18" s="14"/>
+      <c r="J18" s="13"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I19" s="14"/>
+      <c r="J19" s="13"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Manual/source/tab/connectors.xlsx
+++ b/Manual/source/tab/connectors.xlsx
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="509">
   <si>
     <t xml:space="preserve">Toto je sešit se zdrojovými tabulkami popisu konektorů TGZ/TGS v češtině. Každý list odpovídá jednomu unikátnímu typu konektoru. Jelikož se často konektory v rámci TGZ opakují (typicky ty na řídicií desce), jsou zde jen jednou. Tj. Např. IO konektor 22pin weidmuller B2CF se používá pořád dokola, je zde tedy zanesen jen jednou jako „X8_IO_22pin_B2CF“</t>
   </si>
@@ -298,27 +298,51 @@
     <t xml:space="preserve">#X3_DO_4pin_BCZ</t>
   </si>
   <si>
+    <t xml:space="preserve">#X4_ACIN_4pin_TGS560_25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X4_TGS560_24V_5pin_BCZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X1_DC_6pin_TGS560_25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BR_RES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X5_RBR_3pin_TGS560_25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIP-SWITCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#S1_TGS560_DIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X2_ACIN_7pin_2636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X6_TGS560_50_DCbus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X3_24V_BLF_2_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAN-SWITCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#S1_SWITCH_CAN</t>
+  </si>
+  <si>
     <t xml:space="preserve">DI</t>
   </si>
   <si>
-    <t xml:space="preserve">TERM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TGM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#X3_24V_BLF_2_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAN-SWITCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#S1_SWITCH_CAN</t>
-  </si>
-  <si>
     <t xml:space="preserve">#X5_DI_10pin_B2CF</t>
   </si>
   <si>
@@ -419,6 +443,33 @@
   </si>
   <si>
     <t xml:space="preserve">kabelové oko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BVZ 7.62HP/04/180F SN BK BX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BVZ 7.62HP/06/180F SN BK BX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLZ 7.62HP/03/180F SN BK BX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DS03-254-04BE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same Sky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCZ 3.81/05/180F SN OR BX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2636-1107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLF 5.00HC/06/180F SN OR BX           </t>
   </si>
   <si>
     <t xml:space="preserve">helping series</t>
@@ -910,6 +961,9 @@
     <t xml:space="preserve">0V napájení řízení</t>
   </si>
   <si>
+    <t xml:space="preserve">TERM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Teplotní čidlo PT1000</t>
   </si>
   <si>
@@ -1580,9 +1634,6 @@
   </si>
   <si>
     <t xml:space="preserve">Zelená LED</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t xml:space="preserve">trvalý svit</t>
@@ -1945,7 +1996,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K178"/>
+  <dimension ref="A1:K180"/>
   <sheetFormatPr defaultColWidth="12.2734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.82"/>
@@ -3594,17 +3645,17 @@
       <c r="H59" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="I59" s="6" t="e">
+      <c r="I59" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H59, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J59" s="6" t="e">
+        <v>BLF 5.00HC/06/180F SN OR BX           </v>
+      </c>
+      <c r="J59" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H59, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K59" s="6" t="e">
+        <v>Weidmüller</v>
+      </c>
+      <c r="K59" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H59, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6422,17 +6473,20 @@
       <c r="G159" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I159" s="6" t="e">
+      <c r="H159" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I159" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H159, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J159" s="6" t="e">
+        <v>BVZ 7.62HP/04/180F SN BK BX </v>
+      </c>
+      <c r="J159" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H159, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K159" s="6" t="e">
+        <v>Weidmüller</v>
+      </c>
+      <c r="K159" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H159, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6442,19 +6496,22 @@
       <c r="E160" s="4"/>
       <c r="F160" s="4"/>
       <c r="G160" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I160" s="6" t="e">
+        <v>16</v>
+      </c>
+      <c r="H160" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I160" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H160, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J160" s="6" t="e">
+        <v>BCZ 3.81/05/180F SN OR BX </v>
+      </c>
+      <c r="J160" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H160, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K160" s="6" t="e">
+        <v>Weidmüller</v>
+      </c>
+      <c r="K160" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H160, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6464,47 +6521,47 @@
       <c r="E161" s="4"/>
       <c r="F161" s="4"/>
       <c r="G161" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I161" s="6" t="e">
+        <v>67</v>
+      </c>
+      <c r="H161" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I161" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H161, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J161" s="6" t="e">
+        <v>BVZ 7.62HP/06/180F SN BK BX </v>
+      </c>
+      <c r="J161" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H161, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K161" s="6" t="e">
+        <v>Weidmüller</v>
+      </c>
+      <c r="K161" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H161, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
-      <c r="D162" s="4" t="n">
-        <v>560</v>
-      </c>
-      <c r="E162" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F162" s="4" t="n">
-        <v>100</v>
-      </c>
+      <c r="D162" s="4"/>
+      <c r="E162" s="4"/>
+      <c r="F162" s="4"/>
       <c r="G162" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I162" s="6" t="e">
+        <v>74</v>
+      </c>
+      <c r="H162" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I162" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H162, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J162" s="6" t="e">
+        <v>BLZ 7.62HP/03/180F SN BK BX </v>
+      </c>
+      <c r="J162" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H162, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K162" s="6" t="e">
+        <v>Weidmüller</v>
+      </c>
+      <c r="K162" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H162, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6514,19 +6571,22 @@
       <c r="E163" s="4"/>
       <c r="F163" s="4"/>
       <c r="G163" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I163" s="6" t="e">
+        <v>76</v>
+      </c>
+      <c r="H163" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I163" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H163, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J163" s="6" t="e">
+        <v>DS03-254-04BE </v>
+      </c>
+      <c r="J163" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H163, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K163" s="6" t="e">
+        <v>Same Sky</v>
+      </c>
+      <c r="K163" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H163, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6538,31 +6598,52 @@
       <c r="G164" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I164" s="6" t="e">
+      <c r="H164" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I164" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H164, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J164" s="6" t="e">
+        <v>BCZ 3.81/04/180 SN BK BX </v>
+      </c>
+      <c r="J164" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H164, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K164" s="6" t="e">
+        <v>Weidmüller</v>
+      </c>
+      <c r="K164" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H164, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
-      <c r="D165" s="4"/>
-      <c r="E165" s="4"/>
-      <c r="F165" s="4"/>
+      <c r="D165" s="4" t="n">
+        <v>560</v>
+      </c>
+      <c r="E165" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>100</v>
+      </c>
       <c r="G165" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I165" s="6"/>
-      <c r="J165" s="6"/>
-      <c r="K165" s="6"/>
+        <v>49</v>
+      </c>
+      <c r="H165" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I165" s="6" t="str">
+        <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H165, conns!$A$2:$A$501, 0))</f>
+        <v>2636-1107</v>
+      </c>
+      <c r="J165" s="6" t="str">
+        <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H165, conns!$A$2:$A$501, 0))</f>
+        <v>Wago</v>
+      </c>
+      <c r="K165" s="6" t="n">
+        <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H165, conns!$A$2:$A$501, 0))</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B166" s="3"/>
@@ -6571,11 +6652,23 @@
       <c r="E166" s="4"/>
       <c r="F166" s="4"/>
       <c r="G166" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I166" s="6"/>
-      <c r="J166" s="6"/>
-      <c r="K166" s="6"/>
+        <v>67</v>
+      </c>
+      <c r="H166" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I166" s="6" t="str">
+        <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H166, conns!$A$2:$A$501, 0))</f>
+        <v>kabelové oko</v>
+      </c>
+      <c r="J166" s="6" t="str">
+        <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H166, conns!$A$2:$A$501, 0))</f>
+        <v>-</v>
+      </c>
+      <c r="K166" s="6" t="n">
+        <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H166, conns!$A$2:$A$501, 0))</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B167" s="3"/>
@@ -6584,31 +6677,39 @@
       <c r="E167" s="4"/>
       <c r="F167" s="4"/>
       <c r="G167" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I167" s="6"/>
-      <c r="J167" s="6"/>
-      <c r="K167" s="6"/>
+        <v>69</v>
+      </c>
+      <c r="H167" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I167" s="6" t="str">
+        <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H167, conns!$A$2:$A$501, 0))</f>
+        <v>BCZ 3.81/04/180 SN BK BX </v>
+      </c>
+      <c r="J167" s="6" t="str">
+        <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H167, conns!$A$2:$A$501, 0))</f>
+        <v>Weidmüller</v>
+      </c>
+      <c r="K167" s="6" t="n">
+        <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H167, conns!$A$2:$A$501, 0))</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B168" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C168" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D168" s="3"/>
-      <c r="E168" s="3"/>
-      <c r="F168" s="3"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="4"/>
+      <c r="E168" s="4"/>
+      <c r="F168" s="4"/>
       <c r="G168" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H168" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I168" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H168, conns!$A$2:$A$501, 0))</f>
-        <v>BLF 2.50/04/180 SN OR BX </v>
+        <v>BCZ 3.81/05/180F SN OR BX </v>
       </c>
       <c r="J168" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H168, conns!$A$2:$A$501, 0))</f>
@@ -6616,28 +6717,28 @@
       </c>
       <c r="K168" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H168, conns!$A$2:$A$501, 0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B169" s="4"/>
+      <c r="B169" s="3"/>
       <c r="C169" s="3"/>
-      <c r="D169" s="3"/>
-      <c r="E169" s="3"/>
-      <c r="F169" s="3"/>
+      <c r="D169" s="4"/>
+      <c r="E169" s="4"/>
+      <c r="F169" s="4"/>
       <c r="G169" s="1" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="H169" s="5" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="I169" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H169, conns!$A$2:$A$501, 0))</f>
-        <v>B2CF 3.50/04/180 SN OR BX </v>
+        <v>DS03-254-04BE </v>
       </c>
       <c r="J169" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H169, conns!$A$2:$A$501, 0))</f>
-        <v>Weidmüller</v>
+        <v>Same Sky</v>
       </c>
       <c r="K169" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H169, conns!$A$2:$A$501, 0))</f>
@@ -6645,45 +6746,49 @@
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B170" s="4"/>
-      <c r="C170" s="3"/>
+      <c r="B170" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
       <c r="G170" s="1" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I170" s="6" t="e">
+        <v>82</v>
+      </c>
+      <c r="I170" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H170, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J170" s="6" t="e">
+        <v>BLF 2.50/04/180 SN OR BX </v>
+      </c>
+      <c r="J170" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H170, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K170" s="6" t="e">
+        <v>Weidmüller</v>
+      </c>
+      <c r="K170" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H170, conns!$A$2:$A$501, 0))</f>
-        <v>#N/A</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B171" s="4"/>
+      <c r="B171" s="3"/>
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
       <c r="G171" s="1" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="H171" s="5" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="I171" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H171, conns!$A$2:$A$501, 0))</f>
-        <v>B2CF 3.50/10/180 SN OR BX </v>
+        <v>B2CF 3.50/04/180 SN OR BX </v>
       </c>
       <c r="J171" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H171, conns!$A$2:$A$501, 0))</f>
@@ -6691,51 +6796,49 @@
       </c>
       <c r="K171" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H171, conns!$A$2:$A$501, 0))</f>
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B172" s="4"/>
+      <c r="B172" s="3"/>
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
       <c r="G172" s="1" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="H172" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="I172" s="6" t="str">
+        <v>84</v>
+      </c>
+      <c r="I172" s="6" t="e">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H172, conns!$A$2:$A$501, 0))</f>
-        <v>B2CF 3.50/10/180 SN OR BX </v>
-      </c>
-      <c r="J172" s="6" t="str">
+        <v>#N/A</v>
+      </c>
+      <c r="J172" s="6" t="e">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H172, conns!$A$2:$A$501, 0))</f>
-        <v>Weidmüller</v>
-      </c>
-      <c r="K172" s="6" t="n">
+        <v>#N/A</v>
+      </c>
+      <c r="K172" s="6" t="e">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H172, conns!$A$2:$A$501, 0))</f>
-        <v>10</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B173" s="4"/>
-      <c r="C173" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
       <c r="G173" s="1" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I173" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H173, conns!$A$2:$A$501, 0))</f>
-        <v>BCZ 3.81/05/180 SN OR BX </v>
+        <v>B2CF 3.50/10/180 SN OR BX </v>
       </c>
       <c r="J173" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H173, conns!$A$2:$A$501, 0))</f>
@@ -6743,24 +6846,24 @@
       </c>
       <c r="K173" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H173, conns!$A$2:$A$501, 0))</f>
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B174" s="4"/>
-      <c r="C174" s="4"/>
+      <c r="B174" s="3"/>
+      <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
       <c r="G174" s="1" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="H174" s="5" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="I174" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H174, conns!$A$2:$A$501, 0))</f>
-        <v>B2CF 3.50/04/180 SN OR BX </v>
+        <v>B2CF 3.50/10/180 SN OR BX </v>
       </c>
       <c r="J174" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H174, conns!$A$2:$A$501, 0))</f>
@@ -6768,24 +6871,26 @@
       </c>
       <c r="K174" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H174, conns!$A$2:$A$501, 0))</f>
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B175" s="4"/>
-      <c r="C175" s="4"/>
+      <c r="B175" s="3"/>
+      <c r="C175" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
       <c r="G175" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H175" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="H175" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="I175" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H175, conns!$A$2:$A$501, 0))</f>
-        <v>B2CF 3.50/22/180 SN OR BX</v>
+        <v>BCZ 3.81/05/180 SN OR BX </v>
       </c>
       <c r="J175" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H175, conns!$A$2:$A$501, 0))</f>
@@ -6793,24 +6898,24 @@
       </c>
       <c r="K175" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H175, conns!$A$2:$A$501, 0))</f>
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B176" s="4"/>
-      <c r="C176" s="4"/>
+      <c r="B176" s="3"/>
+      <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
       <c r="G176" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H176" s="5" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="I176" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H176, conns!$A$2:$A$501, 0))</f>
-        <v>BCZ 3.81/08/180 SN OR BX </v>
+        <v>B2CF 3.50/04/180 SN OR BX </v>
       </c>
       <c r="J176" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H176, conns!$A$2:$A$501, 0))</f>
@@ -6818,24 +6923,24 @@
       </c>
       <c r="K176" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H176, conns!$A$2:$A$501, 0))</f>
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B177" s="4"/>
-      <c r="C177" s="4"/>
+      <c r="B177" s="3"/>
+      <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
       <c r="F177" s="3"/>
       <c r="G177" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H177" s="5" t="s">
-        <v>83</v>
+        <v>18</v>
+      </c>
+      <c r="H177" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I177" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H177, conns!$A$2:$A$501, 0))</f>
-        <v>BCZ 3.81/08/180 SN OR BX </v>
+        <v>B2CF 3.50/22/180 SN OR BX</v>
       </c>
       <c r="J177" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H177, conns!$A$2:$A$501, 0))</f>
@@ -6843,24 +6948,24 @@
       </c>
       <c r="K177" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H177, conns!$A$2:$A$501, 0))</f>
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B178" s="4"/>
-      <c r="C178" s="4"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
       <c r="F178" s="3"/>
       <c r="G178" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H178" s="5" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I178" s="6" t="str">
         <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H178, conns!$A$2:$A$501, 0))</f>
-        <v>BCZ 3.81/12/180 SN OR BX </v>
+        <v>BCZ 3.81/08/180 SN OR BX </v>
       </c>
       <c r="J178" s="6" t="str">
         <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H178, conns!$A$2:$A$501, 0))</f>
@@ -6868,6 +6973,56 @@
       </c>
       <c r="K178" s="6" t="n">
         <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H178, conns!$A$2:$A$501, 0))</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B179" s="3"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="3"/>
+      <c r="F179" s="3"/>
+      <c r="G179" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H179" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I179" s="6" t="str">
+        <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H179, conns!$A$2:$A$501, 0))</f>
+        <v>BCZ 3.81/08/180 SN OR BX </v>
+      </c>
+      <c r="J179" s="6" t="str">
+        <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H179, conns!$A$2:$A$501, 0))</f>
+        <v>Weidmüller</v>
+      </c>
+      <c r="K179" s="6" t="n">
+        <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H179, conns!$A$2:$A$501, 0))</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="3"/>
+      <c r="F180" s="3"/>
+      <c r="G180" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H180" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I180" s="6" t="str">
+        <f aca="false">INDEX(conns!$B$2:$B$501, MATCH(H180, conns!$A$2:$A$501, 0))</f>
+        <v>BCZ 3.81/12/180 SN OR BX </v>
+      </c>
+      <c r="J180" s="6" t="str">
+        <f aca="false">INDEX(conns!$C$2:$C$501, MATCH(H180, conns!$A$2:$A$501, 0))</f>
+        <v>Weidmüller</v>
+      </c>
+      <c r="K180" s="6" t="n">
+        <f aca="false">INDEX(conns!$D$2:$D$501, MATCH(H180, conns!$A$2:$A$501, 0))</f>
         <v>12</v>
       </c>
     </row>
@@ -6917,20 +7072,20 @@
     <mergeCell ref="F136:F144"/>
     <mergeCell ref="E145:E155"/>
     <mergeCell ref="F145:F155"/>
-    <mergeCell ref="B156:B167"/>
-    <mergeCell ref="C156:C167"/>
+    <mergeCell ref="B156:B169"/>
+    <mergeCell ref="C156:C169"/>
     <mergeCell ref="D156:D158"/>
     <mergeCell ref="E156:E158"/>
     <mergeCell ref="F156:F158"/>
-    <mergeCell ref="D159:D161"/>
-    <mergeCell ref="E159:E161"/>
-    <mergeCell ref="F159:F161"/>
-    <mergeCell ref="D162:D167"/>
-    <mergeCell ref="E162:E167"/>
-    <mergeCell ref="F162:F167"/>
-    <mergeCell ref="B168:B178"/>
-    <mergeCell ref="C168:F172"/>
-    <mergeCell ref="C173:F178"/>
+    <mergeCell ref="D159:D164"/>
+    <mergeCell ref="E159:E164"/>
+    <mergeCell ref="F159:F164"/>
+    <mergeCell ref="D165:D169"/>
+    <mergeCell ref="E165:E169"/>
+    <mergeCell ref="F165:F169"/>
+    <mergeCell ref="B170:B180"/>
+    <mergeCell ref="C170:F174"/>
+    <mergeCell ref="C175:F180"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H9" location="X1_24V_5pin_Microlock!A1" display="#X1_24V_5pin_Microlock"/>
@@ -7077,17 +7232,28 @@
     <hyperlink ref="H156" location="X1_ACIN_PC5!A1" display="#X1_ACIN_PC5"/>
     <hyperlink ref="H157" location="X2_DC_8pin_PC5!A1" display="#X2_DC_8pin_PC5"/>
     <hyperlink ref="H158" location="X3_DO_4pin_BCZ!A1" display="#X3_DO_4pin_BCZ"/>
-    <hyperlink ref="H168" location="X3_24V_BLF_2_5!A1" display="#X3_24V_BLF_2_5"/>
-    <hyperlink ref="H169" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
-    <hyperlink ref="H170" location="S1_SWITCH_CAN!A1" display="#S1_SWITCH_CAN"/>
-    <hyperlink ref="H171" location="X5_DI_10pin_B2CF!A1" display="#X5_DI_10pin_B2CF"/>
-    <hyperlink ref="H172" location="X10_DO_10pin_B2CF!A1" display="#X10_DO_10pin_B2CF"/>
-    <hyperlink ref="H173" location="X1_24V_5pin_BCZ_TGM!A1" display="#X1_24V_5pin_BCZ_TGM"/>
-    <hyperlink ref="H174" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
-    <hyperlink ref="H175" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
-    <hyperlink ref="H176" location="X6_FB1_8pin_B2CF_TGM!A1" display="#X6_FB1_8pin_B2CF_TGM"/>
-    <hyperlink ref="H177" location="X7_FB2_8pin_B2CF_TGM!A1" display="#X7_FB2_8pin_B2CF_TGM"/>
-    <hyperlink ref="H178" location="X5_FBE_12pin_B2CF_TGM!A1" display="#X5_FBE_12pin_B2CF_TGM"/>
+    <hyperlink ref="H159" location="X4_ACIN_4pin_TGS560_25!A1" display="#X4_ACIN_4pin_TGS560_25"/>
+    <hyperlink ref="H160" location="X4_TGS560_24V_5pin_BCZ!A1" display="#X4_TGS560_24V_5pin_BCZ"/>
+    <hyperlink ref="H161" location="X1_DC_6pin_TGS560_25!A1" display="#X1_DC_6pin_TGS560_25"/>
+    <hyperlink ref="H162" location="X5_RBR_3pin_TGS560_25!A1" display="#X5_RBR_3pin_TGS560_25"/>
+    <hyperlink ref="H163" location="S1_TGS560_DIP!A1" display="#S1_TGS560_DIP"/>
+    <hyperlink ref="H164" location="X3_DO_4pin_BCZ!A1" display="#X3_DO_4pin_BCZ"/>
+    <hyperlink ref="H165" location="X2_ACIN_7pin_2636!A1" display="#X2_ACIN_7pin_2636"/>
+    <hyperlink ref="H166" location="X6_TGS560_50_DCbus!A1" display="#X6_TGS560_50_DCbus"/>
+    <hyperlink ref="H167" location="X3_DO_4pin_BCZ!A1" display="#X3_DO_4pin_BCZ"/>
+    <hyperlink ref="H168" location="X4_TGS560_24V_5pin_BCZ!A1" display="#X4_TGS560_24V_5pin_BCZ"/>
+    <hyperlink ref="H169" location="S1_TGS560_DIP!A1" display="#S1_TGS560_DIP"/>
+    <hyperlink ref="H170" location="X3_24V_BLF_2_5!A1" display="#X3_24V_BLF_2_5"/>
+    <hyperlink ref="H171" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H172" location="S1_SWITCH_CAN!A1" display="#S1_SWITCH_CAN"/>
+    <hyperlink ref="H173" location="X5_DI_10pin_B2CF!A1" display="#X5_DI_10pin_B2CF"/>
+    <hyperlink ref="H174" location="X10_DO_10pin_B2CF!A1" display="#X10_DO_10pin_B2CF"/>
+    <hyperlink ref="H175" location="X1_24V_5pin_BCZ_TGM!A1" display="#X1_24V_5pin_BCZ_TGM"/>
+    <hyperlink ref="H176" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H177" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H178" location="X6_FB1_8pin_B2CF_TGM!A1" display="#X6_FB1_8pin_B2CF_TGM"/>
+    <hyperlink ref="H179" location="X7_FB2_8pin_B2CF_TGM!A1" display="#X7_FB2_8pin_B2CF_TGM"/>
+    <hyperlink ref="H180" location="X5_FBE_12pin_B2CF_TGM!A1" display="#X5_FBE_12pin_B2CF_TGM"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -7114,16 +7280,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7131,13 +7297,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7145,13 +7311,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7159,13 +7325,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7173,13 +7339,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7187,13 +7353,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7201,13 +7367,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7215,13 +7381,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7229,13 +7395,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7267,16 +7433,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7284,13 +7450,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7298,13 +7464,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7312,13 +7478,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7326,13 +7492,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7340,13 +7506,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7354,13 +7520,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7392,16 +7558,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7409,13 +7575,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7423,13 +7589,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7437,13 +7603,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7451,13 +7617,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7465,13 +7631,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7479,13 +7645,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7517,16 +7683,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7534,13 +7700,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7548,13 +7714,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7562,13 +7728,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7576,13 +7742,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7590,13 +7756,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -7625,16 +7791,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7642,13 +7808,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7656,13 +7822,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7694,16 +7860,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7711,13 +7877,13 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7725,13 +7891,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7739,13 +7905,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7777,16 +7943,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7794,13 +7960,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7808,13 +7974,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7822,13 +7988,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7836,13 +8002,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -7871,16 +8037,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7888,13 +8054,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7902,13 +8068,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7916,13 +8082,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7954,16 +8120,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7971,13 +8137,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7985,13 +8151,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7999,13 +8165,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8013,13 +8179,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8051,16 +8217,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8068,13 +8234,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8082,13 +8248,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8096,13 +8262,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8110,13 +8276,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8152,7 +8318,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -8161,7 +8327,7 @@
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8172,7 +8338,7 @@
         <v>5055700501</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>5</v>
@@ -8183,10 +8349,10 @@
         <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>22</v>
@@ -8197,10 +8363,10 @@
         <v>21</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>4</v>
@@ -8211,10 +8377,10 @@
         <v>23</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>8</v>
@@ -8225,10 +8391,10 @@
         <v>25</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>8</v>
@@ -8239,10 +8405,10 @@
         <v>27</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>12</v>
@@ -8253,10 +8419,10 @@
         <v>34</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>5</v>
@@ -8267,10 +8433,10 @@
         <v>35</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>6</v>
@@ -8281,10 +8447,10 @@
         <v>37</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>6</v>
@@ -8295,10 +8461,10 @@
         <v>38</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>2</v>
@@ -8309,10 +8475,10 @@
         <v>44</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>6</v>
@@ -8323,10 +8489,10 @@
         <v>46</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>10</v>
@@ -8337,10 +8503,10 @@
         <v>48</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>6</v>
@@ -8351,10 +8517,10 @@
         <v>50</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>12</v>
@@ -8365,10 +8531,10 @@
         <v>57</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>2</v>
@@ -8379,10 +8545,10 @@
         <v>58</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>2</v>
@@ -8393,7 +8559,7 @@
         <v>59</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>65</v>
@@ -8407,7 +8573,7 @@
         <v>61</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>65</v>
@@ -8421,7 +8587,7 @@
         <v>63</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>65</v>
@@ -8435,10 +8601,10 @@
         <v>66</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>8</v>
@@ -8449,10 +8615,10 @@
         <v>68</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>8</v>
@@ -8463,10 +8629,10 @@
         <v>70</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>4</v>
@@ -8474,13 +8640,13 @@
     </row>
     <row r="24" customFormat="false" ht="13.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>4</v>
@@ -8491,10 +8657,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>4</v>
@@ -8502,13 +8668,13 @@
     </row>
     <row r="26" customFormat="false" ht="13.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>10</v>
@@ -8516,13 +8682,13 @@
     </row>
     <row r="27" customFormat="false" ht="13.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>10</v>
@@ -8530,13 +8696,13 @@
     </row>
     <row r="28" customFormat="false" ht="13.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>5</v>
@@ -8547,10 +8713,10 @@
         <v>47</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>3</v>
@@ -8558,13 +8724,13 @@
     </row>
     <row r="30" customFormat="false" ht="13.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>8</v>
@@ -8572,13 +8738,13 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>8</v>
@@ -8586,13 +8752,13 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>12</v>
@@ -8603,7 +8769,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>65</v>
@@ -8617,7 +8783,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>65</v>
@@ -8631,7 +8797,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>65</v>
@@ -8645,7 +8811,7 @@
         <v>39</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>65</v>
@@ -8659,7 +8825,7 @@
         <v>40</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>65</v>
@@ -8673,7 +8839,7 @@
         <v>41</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>65</v>
@@ -8690,7 +8856,7 @@
         <v>52</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>6</v>
@@ -8704,7 +8870,7 @@
         <v>52</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>6</v>
@@ -8718,15 +8884,127 @@
         <v>56</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>6</v>
+      </c>
+    </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8850,6 +9128,14 @@
     <hyperlink ref="A39" location="X3_M1_6pin_BLZ__7_62!A1" display="#X3_M1_6pin_BLZ__7_62"/>
     <hyperlink ref="A40" location="X4_M2_6pin_BLZ__7_62!A1" display="#X4_M2_6pin_BLZ__7_62"/>
     <hyperlink ref="A41" location="X2_560_DC_3pin_BLZ__7_62!A1" display="#X2_560_DC_3pin_BLZ__7_62"/>
+    <hyperlink ref="A42" location="X4_ACIN_4pin_TGS560_25!A1" display="#X4_ACIN_4pin_TGS560_25"/>
+    <hyperlink ref="A43" location="X1_DC_6pin_TGS560_25!A1" display="#X1_DC_6pin_TGS560_25"/>
+    <hyperlink ref="A44" location="X5_RBR_3pin_TGS560_25!A1" display="#X5_RBR_3pin_TGS560_25"/>
+    <hyperlink ref="A45" location="S1_TGS560_DIP!A1" display="#S1_TGS560_DIP"/>
+    <hyperlink ref="A46" location="X4_TGS560_24V_5pin_BCZ!A1" display="#X4_TGS560_24V_5pin_BCZ"/>
+    <hyperlink ref="A47" location="X2_ACIN_7pin_2636!A1" display="#X2_ACIN_7pin_2636"/>
+    <hyperlink ref="A48" location="X6_TGS560_50_DCbus!A1" display="#X6_TGS560_50_DCbus"/>
+    <hyperlink ref="A49" location="XBR_BR_6pin_BLF!A1" display="#XBR_BR_6pin_BLF"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -8876,16 +9162,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8893,13 +9179,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8907,13 +9193,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8921,13 +9207,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8935,13 +9221,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8949,13 +9235,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8963,13 +9249,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9002,16 +9288,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9019,13 +9305,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9033,13 +9319,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9047,13 +9333,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9061,13 +9347,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9075,13 +9361,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -9111,16 +9397,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9128,13 +9414,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9142,13 +9428,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9156,13 +9442,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9170,13 +9456,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -9206,16 +9492,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9223,13 +9509,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9237,13 +9523,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9251,13 +9537,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9265,13 +9551,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -9301,16 +9587,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9318,13 +9604,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>280</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9332,13 +9618,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>72</v>
+        <v>280</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -9367,16 +9653,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9384,13 +9670,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9398,13 +9684,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9412,13 +9698,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9426,13 +9712,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9440,13 +9726,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9454,13 +9740,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9492,16 +9778,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9509,13 +9795,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9523,13 +9809,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9537,13 +9823,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9551,13 +9837,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9565,13 +9851,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9579,13 +9865,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9593,13 +9879,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9607,13 +9893,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9621,13 +9907,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9635,13 +9921,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9671,16 +9957,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9688,13 +9974,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9702,13 +9988,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9716,13 +10002,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -9751,16 +10037,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9768,13 +10054,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9782,13 +10068,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9796,13 +10082,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9810,13 +10096,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9824,13 +10110,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9838,13 +10124,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9874,16 +10160,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9891,13 +10177,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9905,13 +10191,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9919,13 +10205,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -9954,16 +10240,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9971,13 +10257,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9985,13 +10271,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9999,13 +10285,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10013,13 +10299,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10027,13 +10313,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -10062,16 +10348,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10079,13 +10365,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10093,13 +10379,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10107,13 +10393,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10121,13 +10407,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10135,13 +10421,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10149,13 +10435,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10187,16 +10473,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10204,13 +10490,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10218,13 +10504,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10232,13 +10518,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10246,13 +10532,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10260,13 +10546,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10274,13 +10560,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10312,16 +10598,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10329,13 +10615,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10343,13 +10629,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10357,13 +10643,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10371,13 +10657,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10385,13 +10671,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10399,13 +10685,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10413,13 +10699,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10427,13 +10713,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10441,13 +10727,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10455,13 +10741,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10469,13 +10755,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10483,13 +10769,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -10518,16 +10804,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10535,13 +10821,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10549,13 +10835,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10614,16 +10900,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10631,13 +10917,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10645,13 +10931,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10659,13 +10945,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10673,13 +10959,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10711,16 +10997,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10728,13 +11014,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10742,13 +11028,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10756,13 +11042,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10770,13 +11056,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10808,16 +11094,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10825,13 +11111,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10839,13 +11125,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10853,13 +11139,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10867,13 +11153,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10905,16 +11191,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10922,13 +11208,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10936,13 +11222,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10950,13 +11236,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10964,13 +11250,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11000,16 +11286,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11017,13 +11303,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11031,13 +11317,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11045,13 +11331,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -11080,16 +11366,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11097,13 +11383,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11111,13 +11397,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11125,13 +11411,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11139,13 +11425,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11153,13 +11439,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11167,13 +11453,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11181,13 +11467,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11195,13 +11481,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11237,16 +11523,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11254,13 +11540,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11268,13 +11554,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -11304,16 +11590,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11321,13 +11607,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11335,13 +11621,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11349,13 +11635,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11363,13 +11649,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -11399,16 +11685,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11416,13 +11702,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11430,13 +11716,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11444,13 +11730,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11458,13 +11744,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -11493,13 +11779,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11507,10 +11793,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11518,10 +11804,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11529,10 +11815,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11540,10 +11826,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11551,10 +11837,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11562,10 +11848,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11573,10 +11859,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11584,10 +11870,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11595,10 +11881,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11606,10 +11892,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11647,13 +11933,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11661,10 +11947,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11672,10 +11958,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11683,10 +11969,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11694,10 +11980,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11705,10 +11991,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11716,10 +12002,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11727,10 +12013,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11738,10 +12024,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11749,10 +12035,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11760,10 +12046,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11801,35 +12087,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11891,16 +12177,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11908,13 +12194,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11922,13 +12208,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11936,13 +12222,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11950,13 +12236,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11964,13 +12250,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -11998,10 +12284,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12009,7 +12295,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12017,7 +12303,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12025,7 +12311,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12033,7 +12319,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12041,7 +12327,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12049,7 +12335,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12057,7 +12343,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12065,7 +12351,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12073,7 +12359,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12081,7 +12367,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12089,7 +12375,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12097,7 +12383,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -12126,13 +12412,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12140,10 +12426,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12151,10 +12437,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12162,10 +12448,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12173,10 +12459,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12184,10 +12470,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12195,10 +12481,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12206,10 +12492,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12217,10 +12503,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12252,13 +12538,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12266,10 +12552,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12277,10 +12563,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12288,10 +12574,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12299,10 +12585,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12310,10 +12596,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12321,10 +12607,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12332,10 +12618,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12343,10 +12629,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12379,19 +12665,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12399,13 +12685,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>65</v>
@@ -12416,13 +12702,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>65</v>
@@ -12433,16 +12719,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12450,16 +12736,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12467,16 +12753,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12484,16 +12770,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12504,7 +12790,7 @@
         <v>65</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>65</v>
@@ -12521,7 +12807,7 @@
         <v>65</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>65</v>
@@ -12535,16 +12821,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12552,16 +12838,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12569,16 +12855,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12586,16 +12872,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12626,16 +12912,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12643,13 +12929,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12657,13 +12943,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12671,13 +12957,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12685,13 +12971,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12699,13 +12985,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12713,13 +12999,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12727,13 +13013,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12741,13 +13027,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12755,13 +13041,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12769,13 +13055,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12783,13 +13069,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12797,13 +13083,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12811,13 +13097,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12825,13 +13111,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12839,13 +13125,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12853,13 +13139,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12867,13 +13153,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12881,13 +13167,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12895,13 +13181,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12909,13 +13195,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12923,13 +13209,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12937,13 +13223,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -12973,19 +13259,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12993,16 +13279,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13010,16 +13296,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13027,16 +13313,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13044,16 +13330,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13061,16 +13347,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13078,16 +13364,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13098,7 +13384,7 @@
         <v>65</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>65</v>
@@ -13115,7 +13401,7 @@
         <v>65</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>65</v>
@@ -13129,16 +13415,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13146,16 +13432,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13188,19 +13474,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13208,16 +13494,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13225,16 +13511,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13242,16 +13528,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13259,16 +13545,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13276,16 +13562,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13293,16 +13579,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13313,7 +13599,7 @@
         <v>65</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>65</v>
@@ -13330,7 +13616,7 @@
         <v>65</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>65</v>
@@ -13344,16 +13630,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13361,16 +13647,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13402,13 +13688,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13416,10 +13702,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13427,10 +13713,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13438,10 +13724,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13449,10 +13735,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13460,10 +13746,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13471,10 +13757,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13482,10 +13768,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13493,10 +13779,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13504,10 +13790,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13515,10 +13801,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13526,10 +13812,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13537,10 +13823,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13572,13 +13858,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13586,10 +13872,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13597,10 +13883,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13608,10 +13894,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13619,10 +13905,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13630,10 +13916,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13641,10 +13927,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13652,10 +13938,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13663,10 +13949,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13674,10 +13960,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13685,10 +13971,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13696,10 +13982,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13707,10 +13993,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13718,10 +14004,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13729,10 +14015,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13740,10 +14026,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13751,10 +14037,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13762,10 +14048,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13773,10 +14059,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -13805,13 +14091,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13819,10 +14105,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13830,10 +14116,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13841,10 +14127,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13852,10 +14138,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13863,10 +14149,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13874,10 +14160,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13885,10 +14171,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13896,10 +14182,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -13928,13 +14214,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13942,10 +14228,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13953,10 +14239,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13964,10 +14250,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13975,10 +14261,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13986,10 +14272,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13997,10 +14283,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14008,10 +14294,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14019,10 +14305,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14030,10 +14316,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14041,10 +14327,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14082,13 +14368,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14096,10 +14382,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14107,10 +14393,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14118,10 +14404,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14129,10 +14415,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14140,10 +14426,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14151,10 +14437,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14162,10 +14448,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14173,10 +14459,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14220,16 +14506,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14237,13 +14523,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14251,13 +14537,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14265,13 +14551,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14279,13 +14565,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14293,13 +14579,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14307,13 +14593,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14321,13 +14607,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14371,16 +14657,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14388,13 +14674,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14402,13 +14688,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14468,16 +14754,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14485,13 +14771,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14499,13 +14785,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14513,13 +14799,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14527,13 +14813,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14541,13 +14827,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -14575,16 +14861,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14592,13 +14878,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14606,13 +14892,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14620,13 +14906,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14634,13 +14920,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -14670,65 +14956,65 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14736,7 +15022,7 @@
         <v>0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="H8" s="14"/>
       <c r="I8" s="13"/>
@@ -14746,7 +15032,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="13"/>
@@ -14756,7 +15042,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H10" s="14"/>
       <c r="I10" s="13"/>
@@ -14766,7 +15052,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="13"/>
@@ -14776,7 +15062,7 @@
         <v>100</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H12" s="14"/>
       <c r="I12" s="13"/>
@@ -14786,7 +15072,7 @@
         <v>101</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="13"/>
@@ -14796,7 +15082,7 @@
         <v>110</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H14" s="14"/>
       <c r="I14" s="13"/>
@@ -14806,7 +15092,7 @@
         <v>111</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H15" s="14"/>
       <c r="I15" s="13"/>
@@ -14816,7 +15102,7 @@
         <v>1000</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H16" s="14"/>
       <c r="I16" s="13"/>
@@ -14826,7 +15112,7 @@
         <v>1001</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H17" s="14"/>
       <c r="I17" s="13"/>
@@ -14836,7 +15122,7 @@
         <v>1010</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="C18" s="10"/>
       <c r="H18" s="14"/>
@@ -14847,7 +15133,7 @@
         <v>1011</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="13"/>
@@ -14857,7 +15143,7 @@
         <v>1100</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="13"/>
@@ -14867,7 +15153,7 @@
         <v>1101</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="13"/>
@@ -14877,7 +15163,7 @@
         <v>1110</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="13"/>
@@ -14887,7 +15173,7 @@
         <v>1111</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H23" s="14"/>
       <c r="I23" s="13"/>
@@ -14919,105 +15205,105 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="H7" s="14"/>
       <c r="I7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H8" s="14"/>
       <c r="I8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="13"/>
@@ -15029,39 +15315,30 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="13"/>
@@ -15124,16 +15401,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15141,13 +15418,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15155,13 +15432,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15169,13 +15446,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15183,13 +15460,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15233,16 +15510,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15250,13 +15527,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15264,13 +15541,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15278,13 +15555,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15292,13 +15569,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15306,13 +15583,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15320,13 +15597,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15364,16 +15641,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15381,13 +15658,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15395,13 +15672,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15409,13 +15686,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15460,26 +15737,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -15508,16 +15785,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15525,13 +15802,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15539,13 +15816,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15553,13 +15830,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15567,13 +15844,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15581,13 +15858,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15595,13 +15872,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15609,13 +15886,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15623,13 +15900,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15637,13 +15914,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15651,13 +15928,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15665,13 +15942,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15679,13 +15956,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15717,16 +15994,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15734,13 +16011,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15748,13 +16025,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15762,13 +16039,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15776,13 +16053,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15790,13 +16067,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15804,13 +16081,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15818,13 +16095,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15832,13 +16109,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
